--- a/risultati/Risultati_Scheduler.xlsx
+++ b/risultati/Risultati_Scheduler.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Hour</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>P_el_in</t>
+  </si>
+  <si>
+    <t>I_el_in</t>
   </si>
   <si>
     <t>P_el_in_tot</t>
@@ -419,10 +422,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P98"/>
+  <dimension ref="A1:Q98"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -471,8 +474,11 @@
       <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2">
         <v>1</v>
       </c>
@@ -483,46 +489,49 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>51.6</v>
+        <v>18.26381000906784</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>39.07533333333333</v>
+        <v>39.07533333285183</v>
       </c>
       <c r="G2">
-        <v>9.7902</v>
+        <v>3.319828470657291</v>
       </c>
       <c r="H2">
-        <v>0.9827999999999999</v>
+        <v>1.03545</v>
       </c>
       <c r="I2">
-        <v>51.1</v>
+        <v>17.76381000906784</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>216.3620271567981</v>
       </c>
       <c r="K2">
-        <v>39.1608</v>
+        <v>0</v>
       </c>
       <c r="L2">
+        <v>13.27931388262916</v>
+      </c>
+      <c r="M2">
         <v>1.17</v>
       </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
       <c r="N2">
         <v>0</v>
       </c>
       <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
         <v>1</v>
       </c>
-      <c r="P2">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16">
+      <c r="Q2">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3">
         <v>2</v>
       </c>
@@ -533,46 +542,49 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>5.74755</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>47.88273333333333</v>
+        <v>41.35971180350913</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.9157233457454435</v>
       </c>
       <c r="H3">
-        <v>0.9827999999999999</v>
+        <v>1.03545</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>5.24755</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>84.15679666490263</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
+        <v>3.662893382981774</v>
+      </c>
+      <c r="M3">
         <v>1.17</v>
       </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3">
         <v>-0</v>
       </c>
       <c r="P3">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
+        <v>1</v>
+      </c>
+      <c r="Q3">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4">
         <v>3</v>
       </c>
@@ -583,46 +595,49 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>20.65087216216216</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>46.89993333333334</v>
+        <v>41.23998514925457</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>3.778331917499999</v>
       </c>
       <c r="H4">
-        <v>0.9827999999999999</v>
+        <v>1.03545</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>20.15087216216216</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>234.671309704783</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
+        <v>15.11332767</v>
+      </c>
+      <c r="M4">
         <v>1.17</v>
       </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4">
         <v>-0</v>
       </c>
       <c r="P4">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16">
+        <v>1</v>
+      </c>
+      <c r="Q4">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5">
         <v>4</v>
       </c>
@@ -633,46 +648,49 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>20.65087216216216</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>45.91713333333334</v>
+        <v>43.98286706675457</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>3.778331917499999</v>
       </c>
       <c r="H5">
-        <v>0.9827999999999999</v>
+        <v>1.03545</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>20.15087216216216</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>234.671309704783</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
+        <v>15.11332767</v>
+      </c>
+      <c r="M5">
         <v>1.17</v>
       </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O5">
         <v>-0</v>
       </c>
       <c r="P5">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16">
+        <v>1</v>
+      </c>
+      <c r="Q5">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6">
         <v>5</v>
       </c>
@@ -683,46 +701,49 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>20.65087216216216</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>44.93433333333334</v>
+        <v>46.72574898425457</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>3.778331917499999</v>
       </c>
       <c r="H6">
-        <v>0.9827999999999999</v>
+        <v>1.03545</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>20.15087216216216</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>234.671309704783</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
+        <v>15.11332767</v>
+      </c>
+      <c r="M6">
         <v>1.17</v>
       </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
       <c r="N6">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O6">
         <v>-0</v>
       </c>
       <c r="P6">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
       <c r="A7">
         <v>6</v>
       </c>
@@ -733,46 +754,49 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>20.65087216216216</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>43.95153333333334</v>
+        <v>49.46863090175457</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>3.778331917499999</v>
       </c>
       <c r="H7">
-        <v>0.9827999999999999</v>
+        <v>1.03545</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>20.15087216216216</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>234.671309704783</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
+        <v>15.11332767</v>
+      </c>
+      <c r="M7">
         <v>1.17</v>
       </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
       <c r="N7">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O7">
         <v>-0</v>
       </c>
       <c r="P7">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16">
+        <v>1</v>
+      </c>
+      <c r="Q7">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
       <c r="A8">
         <v>7</v>
       </c>
@@ -783,46 +807,49 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>20.65087216216216</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>42.96873333333334</v>
+        <v>52.21151281925457</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>3.778331917499999</v>
       </c>
       <c r="H8">
-        <v>0.9827999999999999</v>
+        <v>1.03545</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>20.15087216216216</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>234.671309704783</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
       <c r="L8">
+        <v>15.11332767</v>
+      </c>
+      <c r="M8">
         <v>1.17</v>
       </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
       <c r="N8">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O8">
         <v>-0</v>
       </c>
       <c r="P8">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16">
+        <v>1</v>
+      </c>
+      <c r="Q8">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17">
       <c r="A9">
         <v>8</v>
       </c>
@@ -833,46 +860,49 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>5.74755</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9">
-        <v>41.98593333333334</v>
+        <v>54.95439473675456</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>0.9157233457454435</v>
       </c>
       <c r="H9">
-        <v>0.9827999999999999</v>
+        <v>1.03545</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>5.24755</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>84.15679666490263</v>
       </c>
       <c r="K9">
         <v>0</v>
       </c>
       <c r="L9">
+        <v>3.662893382981774</v>
+      </c>
+      <c r="M9">
         <v>1.17</v>
       </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
       <c r="N9">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O9">
         <v>-0</v>
       </c>
       <c r="P9">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16">
+        <v>1</v>
+      </c>
+      <c r="Q9">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17">
       <c r="A10">
         <v>9</v>
       </c>
@@ -883,46 +913,49 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>20.65087216216216</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10">
-        <v>41.00313333333334</v>
+        <v>54.8346680825</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>3.778331917499999</v>
       </c>
       <c r="H10">
-        <v>0.9827999999999999</v>
+        <v>1.03545</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>20.15087216216216</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>234.671309704783</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
+        <v>15.11332767</v>
+      </c>
+      <c r="M10">
         <v>1.17</v>
       </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
       <c r="N10">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O10">
         <v>-0</v>
       </c>
       <c r="P10">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16">
+        <v>1</v>
+      </c>
+      <c r="Q10">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17">
       <c r="A11">
         <v>10</v>
       </c>
@@ -939,13 +972,13 @@
         <v>0</v>
       </c>
       <c r="F11">
-        <v>40.02033333333334</v>
+        <v>57.57755</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11">
-        <v>0.9827999999999999</v>
+        <v>1.03545</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -957,22 +990,25 @@
         <v>0</v>
       </c>
       <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
         <v>1.17</v>
       </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
       <c r="N11">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O11">
         <v>-0</v>
       </c>
       <c r="P11">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17">
       <c r="A12">
         <v>11</v>
       </c>
@@ -989,13 +1025,13 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>39.03753333333334</v>
+        <v>56.5421</v>
       </c>
       <c r="G12">
         <v>0</v>
       </c>
       <c r="H12">
-        <v>0.9827999999999999</v>
+        <v>1.03545</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -1007,22 +1043,25 @@
         <v>0</v>
       </c>
       <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
         <v>1.17</v>
       </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
       <c r="N12">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O12">
         <v>-0</v>
       </c>
       <c r="P12">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1039,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="F13">
-        <v>38.05473333333334</v>
+        <v>55.50665</v>
       </c>
       <c r="G13">
         <v>0</v>
       </c>
       <c r="H13">
-        <v>0.9827999999999999</v>
+        <v>1.03545</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -1057,22 +1096,25 @@
         <v>0</v>
       </c>
       <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
         <v>1.17</v>
       </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
       <c r="N13">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O13">
         <v>-0</v>
       </c>
       <c r="P13">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1089,13 +1131,13 @@
         <v>0</v>
       </c>
       <c r="F14">
-        <v>37.07193333333334</v>
+        <v>54.4712</v>
       </c>
       <c r="G14">
         <v>0</v>
       </c>
       <c r="H14">
-        <v>0.9827999999999999</v>
+        <v>1.03545</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -1107,22 +1149,25 @@
         <v>0</v>
       </c>
       <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
         <v>1.17</v>
       </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
       <c r="N14">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O14">
         <v>-0</v>
       </c>
       <c r="P14">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1139,13 +1184,13 @@
         <v>0</v>
       </c>
       <c r="F15">
-        <v>36.08913333333334</v>
+        <v>53.43575</v>
       </c>
       <c r="G15">
         <v>0</v>
       </c>
       <c r="H15">
-        <v>0.9827999999999999</v>
+        <v>1.03545</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -1157,22 +1202,25 @@
         <v>0</v>
       </c>
       <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
         <v>1.17</v>
       </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
       <c r="N15">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O15">
         <v>-0</v>
       </c>
       <c r="P15">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16">
+        <v>-0</v>
+      </c>
+      <c r="Q15">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1189,13 +1237,13 @@
         <v>0</v>
       </c>
       <c r="F16">
-        <v>35.10633333333334</v>
+        <v>52.4003</v>
       </c>
       <c r="G16">
         <v>0</v>
       </c>
       <c r="H16">
-        <v>0.9827999999999999</v>
+        <v>1.03545</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -1207,22 +1255,25 @@
         <v>0</v>
       </c>
       <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
         <v>1.17</v>
       </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
       <c r="N16">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O16">
         <v>-0</v>
       </c>
       <c r="P16">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1239,13 +1290,13 @@
         <v>0</v>
       </c>
       <c r="F17">
-        <v>34.12353333333334</v>
+        <v>51.36485</v>
       </c>
       <c r="G17">
         <v>0</v>
       </c>
       <c r="H17">
-        <v>0.9827999999999999</v>
+        <v>1.03545</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -1257,22 +1308,25 @@
         <v>0</v>
       </c>
       <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
         <v>1.17</v>
       </c>
-      <c r="M17">
-        <v>0</v>
-      </c>
       <c r="N17">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O17">
         <v>-0</v>
       </c>
       <c r="P17">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1289,13 +1343,13 @@
         <v>0</v>
       </c>
       <c r="F18">
-        <v>33.14073333333334</v>
+        <v>50.3294</v>
       </c>
       <c r="G18">
         <v>0</v>
       </c>
       <c r="H18">
-        <v>0.9827999999999999</v>
+        <v>1.03545</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -1307,22 +1361,25 @@
         <v>0</v>
       </c>
       <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
         <v>1.17</v>
       </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
       <c r="N18">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O18">
         <v>-0</v>
       </c>
       <c r="P18">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16">
+        <v>-0</v>
+      </c>
+      <c r="Q18">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1339,13 +1396,13 @@
         <v>0</v>
       </c>
       <c r="F19">
-        <v>32.15793333333334</v>
+        <v>49.29395</v>
       </c>
       <c r="G19">
         <v>0</v>
       </c>
       <c r="H19">
-        <v>0.9827999999999999</v>
+        <v>1.03545</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -1357,22 +1414,25 @@
         <v>0</v>
       </c>
       <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
         <v>1.17</v>
       </c>
-      <c r="M19">
-        <v>0</v>
-      </c>
       <c r="N19">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O19">
         <v>-0</v>
       </c>
       <c r="P19">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1389,13 +1449,13 @@
         <v>0</v>
       </c>
       <c r="F20">
-        <v>31.17513333333334</v>
+        <v>48.25850000000001</v>
       </c>
       <c r="G20">
         <v>0</v>
       </c>
       <c r="H20">
-        <v>0.9827999999999999</v>
+        <v>1.03545</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -1407,22 +1467,25 @@
         <v>0</v>
       </c>
       <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
         <v>1.17</v>
       </c>
-      <c r="M20">
-        <v>0</v>
-      </c>
       <c r="N20">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O20">
         <v>-0</v>
       </c>
       <c r="P20">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1439,13 +1502,13 @@
         <v>0</v>
       </c>
       <c r="F21">
-        <v>30.19233333333334</v>
+        <v>47.22305</v>
       </c>
       <c r="G21">
         <v>0</v>
       </c>
       <c r="H21">
-        <v>0.9827999999999999</v>
+        <v>1.03545</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -1457,22 +1520,25 @@
         <v>0</v>
       </c>
       <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
         <v>1.17</v>
       </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
       <c r="N21">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O21">
         <v>-0</v>
       </c>
       <c r="P21">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16">
+        <v>-0</v>
+      </c>
+      <c r="Q21">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1489,13 +1555,13 @@
         <v>0</v>
       </c>
       <c r="F22">
-        <v>29.20953333333334</v>
+        <v>46.1876</v>
       </c>
       <c r="G22">
         <v>0</v>
       </c>
       <c r="H22">
-        <v>0.9827999999999999</v>
+        <v>1.03545</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -1507,22 +1573,25 @@
         <v>0</v>
       </c>
       <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
         <v>1.17</v>
       </c>
-      <c r="M22">
-        <v>0</v>
-      </c>
       <c r="N22">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O22">
         <v>-0</v>
       </c>
       <c r="P22">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1539,13 +1608,13 @@
         <v>0</v>
       </c>
       <c r="F23">
-        <v>28.22673333333334</v>
+        <v>45.15215000000001</v>
       </c>
       <c r="G23">
         <v>0</v>
       </c>
       <c r="H23">
-        <v>0.9668400000000001</v>
+        <v>1.018635</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -1557,22 +1626,25 @@
         <v>0</v>
       </c>
       <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
         <v>1.151</v>
       </c>
-      <c r="M23">
-        <v>0</v>
-      </c>
       <c r="N23">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O23">
         <v>-0</v>
       </c>
       <c r="P23">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1589,13 +1661,13 @@
         <v>0</v>
       </c>
       <c r="F24">
-        <v>27.25989333333334</v>
+        <v>44.133515</v>
       </c>
       <c r="G24">
         <v>0</v>
       </c>
       <c r="H24">
-        <v>0.9508799999999998</v>
+        <v>1.00182</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -1607,22 +1679,25 @@
         <v>0</v>
       </c>
       <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
         <v>1.132</v>
       </c>
-      <c r="M24">
-        <v>0</v>
-      </c>
       <c r="N24">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O24">
         <v>-0</v>
       </c>
       <c r="P24">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16">
+        <v>-0</v>
+      </c>
+      <c r="Q24">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1639,13 +1714,13 @@
         <v>0</v>
       </c>
       <c r="F25">
-        <v>26.30901333333334</v>
+        <v>43.131695</v>
       </c>
       <c r="G25">
         <v>0</v>
       </c>
       <c r="H25">
-        <v>0.93492</v>
+        <v>0.985005</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -1657,22 +1732,25 @@
         <v>0</v>
       </c>
       <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
         <v>1.113</v>
       </c>
-      <c r="M25">
-        <v>0</v>
-      </c>
       <c r="N25">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O25">
         <v>-0</v>
       </c>
       <c r="P25">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1689,13 +1767,13 @@
         <v>0</v>
       </c>
       <c r="F26">
-        <v>25.37409333333334</v>
+        <v>42.14669</v>
       </c>
       <c r="G26">
         <v>0</v>
       </c>
       <c r="H26">
-        <v>0.91896</v>
+        <v>0.9681900000000001</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -1707,22 +1785,25 @@
         <v>0</v>
       </c>
       <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
         <v>1.094</v>
       </c>
-      <c r="M26">
-        <v>0</v>
-      </c>
       <c r="N26">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O26">
         <v>-0</v>
       </c>
       <c r="P26">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1739,13 +1820,13 @@
         <v>0</v>
       </c>
       <c r="F27">
-        <v>24.45513333333334</v>
+        <v>41.1785</v>
       </c>
       <c r="G27">
         <v>0</v>
       </c>
       <c r="H27">
-        <v>0.9029999999999999</v>
+        <v>0.951375</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -1757,22 +1838,25 @@
         <v>0</v>
       </c>
       <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
         <v>1.075</v>
       </c>
-      <c r="M27">
-        <v>0</v>
-      </c>
       <c r="N27">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O27">
         <v>-0</v>
       </c>
       <c r="P27">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16">
+        <v>-0</v>
+      </c>
+      <c r="Q27">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1789,13 +1873,13 @@
         <v>0</v>
       </c>
       <c r="F28">
-        <v>23.55213333333334</v>
+        <v>40.227125</v>
       </c>
       <c r="G28">
         <v>0</v>
       </c>
       <c r="H28">
-        <v>0.8870400000000001</v>
+        <v>0.9345600000000001</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -1807,22 +1891,25 @@
         <v>0</v>
       </c>
       <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
         <v>1.056</v>
       </c>
-      <c r="M28">
-        <v>0</v>
-      </c>
       <c r="N28">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O28">
         <v>-0</v>
       </c>
       <c r="P28">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1839,13 +1926,13 @@
         <v>0</v>
       </c>
       <c r="F29">
-        <v>22.66509333333334</v>
+        <v>39.292565</v>
       </c>
       <c r="G29">
         <v>0</v>
       </c>
       <c r="H29">
-        <v>0.8710799999999999</v>
+        <v>0.9177449999999999</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -1857,22 +1944,25 @@
         <v>0</v>
       </c>
       <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
         <v>1.037</v>
       </c>
-      <c r="M29">
-        <v>0</v>
-      </c>
       <c r="N29">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O29">
         <v>-0</v>
       </c>
       <c r="P29">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16">
+        <v>-0</v>
+      </c>
+      <c r="Q29">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1889,13 +1979,13 @@
         <v>0</v>
       </c>
       <c r="F30">
-        <v>21.79401333333334</v>
+        <v>38.37482</v>
       </c>
       <c r="G30">
         <v>0</v>
       </c>
       <c r="H30">
-        <v>0.85512</v>
+        <v>0.90093</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -1907,22 +1997,25 @@
         <v>0</v>
       </c>
       <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
         <v>1.018</v>
       </c>
-      <c r="M30">
-        <v>0</v>
-      </c>
       <c r="N30">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O30">
         <v>-0</v>
       </c>
       <c r="P30">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16">
+        <v>-0</v>
+      </c>
+      <c r="Q30">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1939,13 +2032,13 @@
         <v>0</v>
       </c>
       <c r="F31">
-        <v>20.93889333333334</v>
+        <v>37.47389</v>
       </c>
       <c r="G31">
         <v>0</v>
       </c>
       <c r="H31">
-        <v>0.83916</v>
+        <v>0.8841150000000001</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -1957,22 +2050,25 @@
         <v>0</v>
       </c>
       <c r="L31">
-        <v>0.999</v>
+        <v>0</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="N31">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O31">
         <v>-0</v>
       </c>
       <c r="P31">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q31">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1989,13 +2085,13 @@
         <v>0</v>
       </c>
       <c r="F32">
-        <v>20.09973333333334</v>
+        <v>36.589775</v>
       </c>
       <c r="G32">
         <v>0</v>
       </c>
       <c r="H32">
-        <v>0.8232</v>
+        <v>0.8673000000000001</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -2007,22 +2103,25 @@
         <v>0</v>
       </c>
       <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
         <v>0.9800000000000001</v>
       </c>
-      <c r="M32">
-        <v>0</v>
-      </c>
       <c r="N32">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O32">
         <v>-0</v>
       </c>
       <c r="P32">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q32">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2039,13 +2138,13 @@
         <v>0</v>
       </c>
       <c r="F33">
-        <v>19.27653333333334</v>
+        <v>35.722475</v>
       </c>
       <c r="G33">
         <v>0</v>
       </c>
       <c r="H33">
-        <v>0.80724</v>
+        <v>0.8504849999999999</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -2057,22 +2156,25 @@
         <v>0</v>
       </c>
       <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
         <v>0.961</v>
       </c>
-      <c r="M33">
-        <v>0</v>
-      </c>
       <c r="N33">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O33">
         <v>-0</v>
       </c>
       <c r="P33">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16">
+        <v>-0</v>
+      </c>
+      <c r="Q33">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2089,13 +2191,13 @@
         <v>0</v>
       </c>
       <c r="F34">
-        <v>18.46929333333334</v>
+        <v>34.87199</v>
       </c>
       <c r="G34">
         <v>0</v>
       </c>
       <c r="H34">
-        <v>0.7912799999999999</v>
+        <v>0.8336699999999999</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -2107,22 +2209,25 @@
         <v>0</v>
       </c>
       <c r="L34">
-        <v>0.9419999999999998</v>
+        <v>0</v>
       </c>
       <c r="M34">
-        <v>0</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="N34">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O34">
         <v>-0</v>
       </c>
       <c r="P34">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q34">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2139,13 +2244,13 @@
         <v>0</v>
       </c>
       <c r="F35">
-        <v>17.67801333333334</v>
+        <v>34.03832</v>
       </c>
       <c r="G35">
         <v>0</v>
       </c>
       <c r="H35">
-        <v>0.77532</v>
+        <v>0.816855</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -2157,22 +2262,25 @@
         <v>0</v>
       </c>
       <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
         <v>0.923</v>
       </c>
-      <c r="M35">
-        <v>0</v>
-      </c>
       <c r="N35">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O35">
         <v>-0</v>
       </c>
       <c r="P35">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q35">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17">
       <c r="A36">
         <v>35</v>
       </c>
@@ -2189,13 +2297,13 @@
         <v>0</v>
       </c>
       <c r="F36">
-        <v>16.90269333333334</v>
+        <v>33.221465</v>
       </c>
       <c r="G36">
         <v>0</v>
       </c>
       <c r="H36">
-        <v>0.7593599999999999</v>
+        <v>0.80004</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -2207,22 +2315,25 @@
         <v>0</v>
       </c>
       <c r="L36">
-        <v>0.9039999999999999</v>
+        <v>0</v>
       </c>
       <c r="M36">
-        <v>0</v>
+        <v>0.904</v>
       </c>
       <c r="N36">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O36">
         <v>-0</v>
       </c>
       <c r="P36">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16">
+        <v>-0</v>
+      </c>
+      <c r="Q36">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17">
       <c r="A37">
         <v>36</v>
       </c>
@@ -2239,13 +2350,13 @@
         <v>0</v>
       </c>
       <c r="F37">
-        <v>16.14333333333334</v>
+        <v>32.421425</v>
       </c>
       <c r="G37">
         <v>0</v>
       </c>
       <c r="H37">
-        <v>0.7433999999999999</v>
+        <v>0.7832250000000001</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -2257,22 +2368,25 @@
         <v>0</v>
       </c>
       <c r="L37">
-        <v>0.8849999999999999</v>
+        <v>0</v>
       </c>
       <c r="M37">
-        <v>0</v>
+        <v>0.8850000000000001</v>
       </c>
       <c r="N37">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O37">
         <v>-0</v>
       </c>
       <c r="P37">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16">
+        <v>-0</v>
+      </c>
+      <c r="Q37">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17">
       <c r="A38">
         <v>37</v>
       </c>
@@ -2289,13 +2403,13 @@
         <v>0</v>
       </c>
       <c r="F38">
-        <v>15.39993333333334</v>
+        <v>31.6382</v>
       </c>
       <c r="G38">
         <v>0</v>
       </c>
       <c r="H38">
-        <v>0.7274400000000001</v>
+        <v>0.7664100000000001</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -2307,22 +2421,25 @@
         <v>0</v>
       </c>
       <c r="L38">
-        <v>0.8660000000000001</v>
+        <v>0</v>
       </c>
       <c r="M38">
-        <v>0</v>
+        <v>0.8660000000000002</v>
       </c>
       <c r="N38">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O38">
         <v>-0</v>
       </c>
       <c r="P38">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q38">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17">
       <c r="A39">
         <v>38</v>
       </c>
@@ -2339,13 +2456,13 @@
         <v>0</v>
       </c>
       <c r="F39">
-        <v>14.67249333333334</v>
+        <v>30.87179</v>
       </c>
       <c r="G39">
         <v>0</v>
       </c>
       <c r="H39">
-        <v>0.71148</v>
+        <v>0.7495950000000001</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -2357,22 +2474,25 @@
         <v>0</v>
       </c>
       <c r="L39">
-        <v>0.847</v>
+        <v>0</v>
       </c>
       <c r="M39">
-        <v>0</v>
+        <v>0.8470000000000002</v>
       </c>
       <c r="N39">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O39">
         <v>-0</v>
       </c>
       <c r="P39">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q39">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17">
       <c r="A40">
         <v>39</v>
       </c>
@@ -2389,13 +2509,13 @@
         <v>0</v>
       </c>
       <c r="F40">
-        <v>13.96101333333334</v>
+        <v>30.122195</v>
       </c>
       <c r="G40">
         <v>0</v>
       </c>
       <c r="H40">
-        <v>0.6955200000000001</v>
+        <v>0.7327800000000002</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -2407,22 +2527,25 @@
         <v>0</v>
       </c>
       <c r="L40">
-        <v>0.8280000000000002</v>
+        <v>0</v>
       </c>
       <c r="M40">
-        <v>0</v>
+        <v>0.8280000000000003</v>
       </c>
       <c r="N40">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O40">
         <v>-0</v>
       </c>
       <c r="P40">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16">
+        <v>-0</v>
+      </c>
+      <c r="Q40">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2439,13 +2562,13 @@
         <v>0</v>
       </c>
       <c r="F41">
-        <v>13.26549333333334</v>
+        <v>29.389415</v>
       </c>
       <c r="G41">
         <v>0</v>
       </c>
       <c r="H41">
-        <v>0.6795600000000001</v>
+        <v>0.7159650000000001</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -2457,22 +2580,25 @@
         <v>0</v>
       </c>
       <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
         <v>0.8090000000000001</v>
       </c>
-      <c r="M41">
-        <v>0</v>
-      </c>
       <c r="N41">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O41">
         <v>-0</v>
       </c>
       <c r="P41">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16">
+        <v>-0</v>
+      </c>
+      <c r="Q41">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17">
       <c r="A42">
         <v>41</v>
       </c>
@@ -2489,13 +2615,13 @@
         <v>0</v>
       </c>
       <c r="F42">
-        <v>12.58593333333334</v>
+        <v>28.67345</v>
       </c>
       <c r="G42">
         <v>0</v>
       </c>
       <c r="H42">
-        <v>0.6636</v>
+        <v>0.69915</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -2507,22 +2633,25 @@
         <v>0</v>
       </c>
       <c r="L42">
-        <v>0.7899999999999999</v>
+        <v>0</v>
       </c>
       <c r="M42">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="N42">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O42">
         <v>-0</v>
       </c>
       <c r="P42">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16">
+        <v>-0</v>
+      </c>
+      <c r="Q42">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17">
       <c r="A43">
         <v>42</v>
       </c>
@@ -2539,13 +2668,13 @@
         <v>0</v>
       </c>
       <c r="F43">
-        <v>11.92233333333334</v>
+        <v>27.9743</v>
       </c>
       <c r="G43">
         <v>0</v>
       </c>
       <c r="H43">
-        <v>0.6686400000000001</v>
+        <v>0.7044600000000001</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -2557,22 +2686,25 @@
         <v>0</v>
       </c>
       <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
         <v>0.7960000000000002</v>
       </c>
-      <c r="M43">
-        <v>0</v>
-      </c>
       <c r="N43">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O43">
         <v>-0</v>
       </c>
       <c r="P43">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q43">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17">
       <c r="A44">
         <v>43</v>
       </c>
@@ -2589,13 +2721,13 @@
         <v>0</v>
       </c>
       <c r="F44">
-        <v>11.25369333333334</v>
+        <v>27.26983999999999</v>
       </c>
       <c r="G44">
         <v>0</v>
       </c>
       <c r="H44">
-        <v>0.6736800000000001</v>
+        <v>0.70977</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -2607,22 +2739,25 @@
         <v>0</v>
       </c>
       <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44">
         <v>0.802</v>
       </c>
-      <c r="M44">
-        <v>0</v>
-      </c>
       <c r="N44">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O44">
         <v>-0</v>
       </c>
       <c r="P44">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q44">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17">
       <c r="A45">
         <v>44</v>
       </c>
@@ -2639,13 +2774,13 @@
         <v>0</v>
       </c>
       <c r="F45">
-        <v>10.58001333333334</v>
+        <v>26.56007</v>
       </c>
       <c r="G45">
         <v>0</v>
       </c>
       <c r="H45">
-        <v>0.6787200000000002</v>
+        <v>0.7150800000000003</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -2657,22 +2792,25 @@
         <v>0</v>
       </c>
       <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
         <v>0.8080000000000003</v>
       </c>
-      <c r="M45">
-        <v>0</v>
-      </c>
       <c r="N45">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O45">
         <v>-0</v>
       </c>
       <c r="P45">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q45">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17">
       <c r="A46">
         <v>45</v>
       </c>
@@ -2689,13 +2827,13 @@
         <v>0</v>
       </c>
       <c r="F46">
-        <v>9.90129333333334</v>
+        <v>25.84499</v>
       </c>
       <c r="G46">
         <v>0</v>
       </c>
       <c r="H46">
-        <v>0.68376</v>
+        <v>0.7203900000000001</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -2707,22 +2845,25 @@
         <v>0</v>
       </c>
       <c r="L46">
-        <v>0.8140000000000001</v>
+        <v>0</v>
       </c>
       <c r="M46">
-        <v>0</v>
+        <v>0.8140000000000002</v>
       </c>
       <c r="N46">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O46">
         <v>-0</v>
       </c>
       <c r="P46">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q46">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17">
       <c r="A47">
         <v>46</v>
       </c>
@@ -2739,13 +2880,13 @@
         <v>0</v>
       </c>
       <c r="F47">
-        <v>9.217533333333341</v>
+        <v>25.12459999999999</v>
       </c>
       <c r="G47">
         <v>0</v>
       </c>
       <c r="H47">
-        <v>0.6888</v>
+        <v>0.7257</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -2757,22 +2898,25 @@
         <v>0</v>
       </c>
       <c r="L47">
-        <v>0.82</v>
+        <v>0</v>
       </c>
       <c r="M47">
-        <v>0</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="N47">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O47">
         <v>-0</v>
       </c>
       <c r="P47">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q47">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17">
       <c r="A48">
         <v>47</v>
       </c>
@@ -2789,13 +2933,13 @@
         <v>0</v>
       </c>
       <c r="F48">
-        <v>8.52873333333334</v>
+        <v>24.39889999999999</v>
       </c>
       <c r="G48">
         <v>0</v>
       </c>
       <c r="H48">
-        <v>0.6938400000000001</v>
+        <v>0.7310100000000002</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -2807,22 +2951,25 @@
         <v>0</v>
       </c>
       <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
         <v>0.8260000000000002</v>
       </c>
-      <c r="M48">
-        <v>0</v>
-      </c>
       <c r="N48">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O48">
         <v>-0</v>
       </c>
       <c r="P48">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q48">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17">
       <c r="A49">
         <v>48</v>
       </c>
@@ -2839,13 +2986,13 @@
         <v>0</v>
       </c>
       <c r="F49">
-        <v>7.834893333333341</v>
+        <v>23.66788999999999</v>
       </c>
       <c r="G49">
         <v>0</v>
       </c>
       <c r="H49">
-        <v>0.6988800000000001</v>
+        <v>0.7363200000000001</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -2857,22 +3004,25 @@
         <v>0</v>
       </c>
       <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
         <v>0.8320000000000001</v>
       </c>
-      <c r="M49">
-        <v>0</v>
-      </c>
       <c r="N49">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O49">
         <v>-0</v>
       </c>
       <c r="P49">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q49">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17">
       <c r="A50">
         <v>49</v>
       </c>
@@ -2889,13 +3039,13 @@
         <v>0</v>
       </c>
       <c r="F50">
-        <v>7.136013333333341</v>
+        <v>22.93156999999999</v>
       </c>
       <c r="G50">
         <v>0</v>
       </c>
       <c r="H50">
-        <v>0.70392</v>
+        <v>0.7416300000000001</v>
       </c>
       <c r="I50">
         <v>0</v>
@@ -2907,22 +3057,25 @@
         <v>0</v>
       </c>
       <c r="L50">
-        <v>0.838</v>
+        <v>0</v>
       </c>
       <c r="M50">
-        <v>0</v>
+        <v>0.8380000000000002</v>
       </c>
       <c r="N50">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O50">
         <v>-0</v>
       </c>
       <c r="P50">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q50">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17">
       <c r="A51">
         <v>50</v>
       </c>
@@ -2939,13 +3092,13 @@
         <v>0</v>
       </c>
       <c r="F51">
-        <v>6.432093333333341</v>
+        <v>22.18993999999999</v>
       </c>
       <c r="G51">
         <v>0</v>
       </c>
       <c r="H51">
-        <v>0.7089600000000001</v>
+        <v>0.7469400000000002</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -2957,22 +3110,25 @@
         <v>0</v>
       </c>
       <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51">
         <v>0.8440000000000002</v>
       </c>
-      <c r="M51">
-        <v>0</v>
-      </c>
       <c r="N51">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O51">
         <v>-0</v>
       </c>
       <c r="P51">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q51">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17">
       <c r="A52">
         <v>51</v>
       </c>
@@ -2989,13 +3145,13 @@
         <v>0</v>
       </c>
       <c r="F52">
-        <v>5.72313333333334</v>
+        <v>21.44299999999999</v>
       </c>
       <c r="G52">
         <v>0</v>
       </c>
       <c r="H52">
-        <v>0.7140000000000002</v>
+        <v>0.7522500000000002</v>
       </c>
       <c r="I52">
         <v>0</v>
@@ -3007,22 +3163,25 @@
         <v>0</v>
       </c>
       <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52">
         <v>0.85</v>
       </c>
-      <c r="M52">
-        <v>0</v>
-      </c>
       <c r="N52">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O52">
         <v>-0</v>
       </c>
       <c r="P52">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q52">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17">
       <c r="A53">
         <v>52</v>
       </c>
@@ -3039,13 +3198,13 @@
         <v>0</v>
       </c>
       <c r="F53">
-        <v>5.00913333333334</v>
+        <v>20.69074999999999</v>
       </c>
       <c r="G53">
         <v>0</v>
       </c>
       <c r="H53">
-        <v>0.7190399999999999</v>
+        <v>0.7575599999999999</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -3057,22 +3216,25 @@
         <v>0</v>
       </c>
       <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53">
         <v>0.8559999999999999</v>
       </c>
-      <c r="M53">
-        <v>0</v>
-      </c>
       <c r="N53">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O53">
         <v>-0</v>
       </c>
       <c r="P53">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q53">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17">
       <c r="A54">
         <v>53</v>
       </c>
@@ -3089,13 +3251,13 @@
         <v>0</v>
       </c>
       <c r="F54">
-        <v>4.29009333333334</v>
+        <v>19.93318999999999</v>
       </c>
       <c r="G54">
         <v>0</v>
       </c>
       <c r="H54">
-        <v>0.7240800000000001</v>
+        <v>0.76287</v>
       </c>
       <c r="I54">
         <v>0</v>
@@ -3107,22 +3269,25 @@
         <v>0</v>
       </c>
       <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="M54">
         <v>0.8620000000000001</v>
       </c>
-      <c r="M54">
-        <v>0</v>
-      </c>
       <c r="N54">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O54">
         <v>-0</v>
       </c>
       <c r="P54">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q54">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17">
       <c r="A55">
         <v>54</v>
       </c>
@@ -3139,13 +3304,13 @@
         <v>0</v>
       </c>
       <c r="F55">
-        <v>3.56601333333334</v>
+        <v>19.17031999999999</v>
       </c>
       <c r="G55">
         <v>0</v>
       </c>
       <c r="H55">
-        <v>0.72912</v>
+        <v>0.76818</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -3157,22 +3322,25 @@
         <v>0</v>
       </c>
       <c r="L55">
+        <v>0</v>
+      </c>
+      <c r="M55">
         <v>0.868</v>
       </c>
-      <c r="M55">
-        <v>0</v>
-      </c>
       <c r="N55">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O55">
         <v>-0</v>
       </c>
       <c r="P55">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="56" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q55">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17">
       <c r="A56">
         <v>55</v>
       </c>
@@ -3183,46 +3351,49 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>34.26898326898323</v>
+        <v>0</v>
       </c>
       <c r="E56">
         <v>0</v>
       </c>
       <c r="F56">
-        <v>2.83689333333334</v>
+        <v>18.40213999999999</v>
       </c>
       <c r="G56">
-        <v>6.423649999999992</v>
+        <v>0</v>
       </c>
       <c r="H56">
-        <v>0.73416</v>
+        <v>0.7734900000000001</v>
       </c>
       <c r="I56">
-        <v>33.76898326898323</v>
+        <v>0</v>
       </c>
       <c r="J56">
         <v>0</v>
       </c>
       <c r="K56">
-        <v>25.69459999999997</v>
+        <v>0</v>
       </c>
       <c r="L56">
-        <v>0.874</v>
+        <v>0</v>
       </c>
       <c r="M56">
-        <v>0</v>
+        <v>0.8740000000000001</v>
       </c>
       <c r="N56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O56">
-        <v>1</v>
+        <v>-0</v>
       </c>
       <c r="P56">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="57" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q56">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17">
       <c r="A57">
         <v>56</v>
       </c>
@@ -3233,46 +3404,49 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>51.6</v>
+        <v>0</v>
       </c>
       <c r="E57">
         <v>0</v>
       </c>
       <c r="F57">
-        <v>8.526383333333333</v>
+        <v>17.62864999999999</v>
       </c>
       <c r="G57">
-        <v>9.7902</v>
+        <v>0</v>
       </c>
       <c r="H57">
-        <v>0.7392000000000001</v>
+        <v>0.7788000000000002</v>
       </c>
       <c r="I57">
-        <v>51.1</v>
+        <v>0</v>
       </c>
       <c r="J57">
         <v>0</v>
       </c>
       <c r="K57">
-        <v>39.1608</v>
+        <v>0</v>
       </c>
       <c r="L57">
-        <v>0.8800000000000001</v>
+        <v>0</v>
       </c>
       <c r="M57">
-        <v>0</v>
+        <v>0.8800000000000002</v>
       </c>
       <c r="N57">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O57">
-        <v>1</v>
+        <v>-0</v>
       </c>
       <c r="P57">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="58" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q57">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17">
       <c r="A58">
         <v>57</v>
       </c>
@@ -3289,13 +3463,13 @@
         <v>0</v>
       </c>
       <c r="F58">
-        <v>17.57738333333333</v>
+        <v>16.84984999999999</v>
       </c>
       <c r="G58">
         <v>0</v>
       </c>
       <c r="H58">
-        <v>0.74424</v>
+        <v>0.78411</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -3307,22 +3481,25 @@
         <v>0</v>
       </c>
       <c r="L58">
+        <v>0</v>
+      </c>
+      <c r="M58">
         <v>0.886</v>
       </c>
-      <c r="M58">
-        <v>0</v>
-      </c>
       <c r="N58">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O58">
         <v>-0</v>
       </c>
       <c r="P58">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="59" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q58">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17">
       <c r="A59">
         <v>58</v>
       </c>
@@ -3339,13 +3516,13 @@
         <v>0</v>
       </c>
       <c r="F59">
-        <v>16.83314333333333</v>
+        <v>16.06573999999999</v>
       </c>
       <c r="G59">
         <v>0</v>
       </c>
       <c r="H59">
-        <v>0.7492799999999999</v>
+        <v>0.78942</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -3357,22 +3534,25 @@
         <v>0</v>
       </c>
       <c r="L59">
-        <v>0.8919999999999999</v>
+        <v>0</v>
       </c>
       <c r="M59">
-        <v>0</v>
+        <v>0.892</v>
       </c>
       <c r="N59">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O59">
         <v>-0</v>
       </c>
       <c r="P59">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="60" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q59">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17">
       <c r="A60">
         <v>59</v>
       </c>
@@ -3389,13 +3569,13 @@
         <v>0</v>
       </c>
       <c r="F60">
-        <v>16.08386333333333</v>
+        <v>15.27631999999999</v>
       </c>
       <c r="G60">
         <v>0</v>
       </c>
       <c r="H60">
-        <v>0.7543200000000001</v>
+        <v>0.7947300000000002</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -3407,22 +3587,25 @@
         <v>0</v>
       </c>
       <c r="L60">
-        <v>0.8980000000000001</v>
+        <v>0</v>
       </c>
       <c r="M60">
-        <v>0</v>
+        <v>0.8980000000000002</v>
       </c>
       <c r="N60">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O60">
         <v>-0</v>
       </c>
       <c r="P60">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="61" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q60">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17">
       <c r="A61">
         <v>60</v>
       </c>
@@ -3439,13 +3622,13 @@
         <v>0</v>
       </c>
       <c r="F61">
-        <v>15.32954333333333</v>
+        <v>14.48159</v>
       </c>
       <c r="G61">
         <v>0</v>
       </c>
       <c r="H61">
-        <v>0.75936</v>
+        <v>0.8000400000000001</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -3457,22 +3640,25 @@
         <v>0</v>
       </c>
       <c r="L61">
-        <v>0.904</v>
+        <v>0</v>
       </c>
       <c r="M61">
-        <v>0</v>
+        <v>0.9040000000000001</v>
       </c>
       <c r="N61">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O61">
         <v>-0</v>
       </c>
       <c r="P61">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="62" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q61">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17">
       <c r="A62">
         <v>61</v>
       </c>
@@ -3489,13 +3675,13 @@
         <v>0</v>
       </c>
       <c r="F62">
-        <v>14.57018333333333</v>
+        <v>13.68154999999999</v>
       </c>
       <c r="G62">
         <v>0</v>
       </c>
       <c r="H62">
-        <v>0.7644</v>
+        <v>0.80535</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -3507,22 +3693,25 @@
         <v>0</v>
       </c>
       <c r="L62">
-        <v>0.9099999999999999</v>
+        <v>0</v>
       </c>
       <c r="M62">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="N62">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O62">
         <v>-0</v>
       </c>
       <c r="P62">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="63" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q62">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17">
       <c r="A63">
         <v>62</v>
       </c>
@@ -3539,13 +3728,13 @@
         <v>0</v>
       </c>
       <c r="F63">
-        <v>13.80578333333333</v>
+        <v>12.87619999999999</v>
       </c>
       <c r="G63">
         <v>0</v>
       </c>
       <c r="H63">
-        <v>0.75348</v>
+        <v>0.7938450000000001</v>
       </c>
       <c r="I63">
         <v>0</v>
@@ -3557,22 +3746,25 @@
         <v>0</v>
       </c>
       <c r="L63">
-        <v>0.897</v>
+        <v>0</v>
       </c>
       <c r="M63">
-        <v>0</v>
+        <v>0.8970000000000001</v>
       </c>
       <c r="N63">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O63">
         <v>-0</v>
       </c>
       <c r="P63">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="64" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q63">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17">
       <c r="A64">
         <v>63</v>
       </c>
@@ -3589,13 +3781,13 @@
         <v>0</v>
       </c>
       <c r="F64">
-        <v>13.05230333333333</v>
+        <v>12.08235499999999</v>
       </c>
       <c r="G64">
         <v>0</v>
       </c>
       <c r="H64">
-        <v>0.74256</v>
+        <v>0.78234</v>
       </c>
       <c r="I64">
         <v>0</v>
@@ -3607,22 +3799,25 @@
         <v>0</v>
       </c>
       <c r="L64">
+        <v>0</v>
+      </c>
+      <c r="M64">
         <v>0.884</v>
       </c>
-      <c r="M64">
-        <v>0</v>
-      </c>
       <c r="N64">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O64">
         <v>-0</v>
       </c>
       <c r="P64">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="65" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q64">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17">
       <c r="A65">
         <v>64</v>
       </c>
@@ -3639,13 +3834,13 @@
         <v>0</v>
       </c>
       <c r="F65">
-        <v>12.30974333333334</v>
+        <v>11.30001499999999</v>
       </c>
       <c r="G65">
         <v>0</v>
       </c>
       <c r="H65">
-        <v>0.73164</v>
+        <v>0.770835</v>
       </c>
       <c r="I65">
         <v>0</v>
@@ -3657,22 +3852,25 @@
         <v>0</v>
       </c>
       <c r="L65">
-        <v>0.871</v>
+        <v>0</v>
       </c>
       <c r="M65">
-        <v>0</v>
+        <v>0.8710000000000001</v>
       </c>
       <c r="N65">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O65">
         <v>-0</v>
       </c>
       <c r="P65">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="66" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q65">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17">
       <c r="A66">
         <v>65</v>
       </c>
@@ -3689,13 +3887,13 @@
         <v>0</v>
       </c>
       <c r="F66">
-        <v>11.57810333333333</v>
+        <v>10.52917999999999</v>
       </c>
       <c r="G66">
         <v>0</v>
       </c>
       <c r="H66">
-        <v>0.72072</v>
+        <v>0.7593300000000001</v>
       </c>
       <c r="I66">
         <v>0</v>
@@ -3707,22 +3905,25 @@
         <v>0</v>
       </c>
       <c r="L66">
-        <v>0.858</v>
+        <v>0</v>
       </c>
       <c r="M66">
-        <v>0</v>
+        <v>0.8580000000000001</v>
       </c>
       <c r="N66">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O66">
         <v>-0</v>
       </c>
       <c r="P66">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="67" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q66">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17">
       <c r="A67">
         <v>66</v>
       </c>
@@ -3739,13 +3940,13 @@
         <v>0</v>
       </c>
       <c r="F67">
-        <v>10.85738333333333</v>
+        <v>9.769849999999993</v>
       </c>
       <c r="G67">
         <v>0</v>
       </c>
       <c r="H67">
-        <v>0.7098</v>
+        <v>0.747825</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -3757,22 +3958,25 @@
         <v>0</v>
       </c>
       <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67">
         <v>0.845</v>
       </c>
-      <c r="M67">
-        <v>0</v>
-      </c>
       <c r="N67">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O67">
         <v>-0</v>
       </c>
       <c r="P67">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="68" spans="1:16">
+        <v>-0</v>
+      </c>
+      <c r="Q67">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17">
       <c r="A68">
         <v>67</v>
       </c>
@@ -3789,13 +3993,13 @@
         <v>0</v>
       </c>
       <c r="F68">
-        <v>10.14758333333334</v>
+        <v>9.022024999999992</v>
       </c>
       <c r="G68">
         <v>0</v>
       </c>
       <c r="H68">
-        <v>0.6988800000000001</v>
+        <v>0.7363200000000001</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -3807,22 +4011,25 @@
         <v>0</v>
       </c>
       <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68">
         <v>0.8320000000000001</v>
       </c>
-      <c r="M68">
-        <v>0</v>
-      </c>
       <c r="N68">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O68">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P68">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="69" spans="1:16">
+        <v>-0</v>
+      </c>
+      <c r="Q68">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17">
       <c r="A69">
         <v>68</v>
       </c>
@@ -3839,13 +4046,13 @@
         <v>0</v>
       </c>
       <c r="F69">
-        <v>9.448703333333334</v>
+        <v>8.285704999999993</v>
       </c>
       <c r="G69">
         <v>0</v>
       </c>
       <c r="H69">
-        <v>0.6879600000000001</v>
+        <v>0.7248150000000002</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -3857,22 +4064,25 @@
         <v>0</v>
       </c>
       <c r="L69">
-        <v>0.8190000000000002</v>
+        <v>0</v>
       </c>
       <c r="M69">
-        <v>0</v>
+        <v>0.8190000000000003</v>
       </c>
       <c r="N69">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O69">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P69">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="70" spans="1:16">
+        <v>-0</v>
+      </c>
+      <c r="Q69">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17">
       <c r="A70">
         <v>69</v>
       </c>
@@ -3883,46 +4093,49 @@
         <v>0</v>
       </c>
       <c r="D70">
-        <v>0</v>
+        <v>14.0939508098809</v>
       </c>
       <c r="E70">
         <v>0</v>
       </c>
       <c r="F70">
-        <v>8.760743333333334</v>
+        <v>7.560889999999993</v>
       </c>
       <c r="G70">
-        <v>0</v>
+        <v>2.518887944999999</v>
       </c>
       <c r="H70">
-        <v>0.67704</v>
+        <v>0.71331</v>
       </c>
       <c r="I70">
-        <v>0</v>
+        <v>13.5939508098809</v>
       </c>
       <c r="J70">
-        <v>0</v>
+        <v>179.9971046617788</v>
       </c>
       <c r="K70">
         <v>0</v>
       </c>
       <c r="L70">
-        <v>0.8059999999999999</v>
+        <v>10.07555178</v>
       </c>
       <c r="M70">
-        <v>0</v>
+        <v>0.806</v>
       </c>
       <c r="N70">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O70">
-        <v>-0</v>
+        <v>1</v>
       </c>
       <c r="P70">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="71" spans="1:16">
+        <v>1</v>
+      </c>
+      <c r="Q70">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17">
       <c r="A71">
         <v>70</v>
       </c>
@@ -3933,46 +4146,49 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>0</v>
+        <v>20.65087216216216</v>
       </c>
       <c r="E71">
         <v>0</v>
       </c>
       <c r="F71">
-        <v>8.083703333333334</v>
+        <v>9.366467944999993</v>
       </c>
       <c r="G71">
-        <v>0</v>
+        <v>3.778331917499999</v>
       </c>
       <c r="H71">
-        <v>0.66612</v>
+        <v>0.701805</v>
       </c>
       <c r="I71">
-        <v>0</v>
+        <v>20.15087216216216</v>
       </c>
       <c r="J71">
-        <v>0</v>
+        <v>234.671309704783</v>
       </c>
       <c r="K71">
         <v>0</v>
       </c>
       <c r="L71">
+        <v>15.11332767</v>
+      </c>
+      <c r="M71">
         <v>0.793</v>
       </c>
-      <c r="M71">
-        <v>0</v>
-      </c>
       <c r="N71">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O71">
         <v>-0</v>
       </c>
       <c r="P71">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="72" spans="1:16">
+        <v>1</v>
+      </c>
+      <c r="Q71">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17">
       <c r="A72">
         <v>71</v>
       </c>
@@ -3983,46 +4199,49 @@
         <v>0</v>
       </c>
       <c r="D72">
-        <v>0</v>
+        <v>20.65087216216216</v>
       </c>
       <c r="E72">
         <v>0</v>
       </c>
       <c r="F72">
-        <v>7.417583333333334</v>
+        <v>12.44299486249999</v>
       </c>
       <c r="G72">
-        <v>0</v>
+        <v>3.778331917499999</v>
       </c>
       <c r="H72">
-        <v>0.6552</v>
+        <v>0.6903</v>
       </c>
       <c r="I72">
-        <v>0</v>
+        <v>20.15087216216216</v>
       </c>
       <c r="J72">
-        <v>0</v>
+        <v>234.671309704783</v>
       </c>
       <c r="K72">
         <v>0</v>
       </c>
       <c r="L72">
+        <v>15.11332767</v>
+      </c>
+      <c r="M72">
         <v>0.78</v>
       </c>
-      <c r="M72">
-        <v>0</v>
-      </c>
       <c r="N72">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O72">
         <v>-0</v>
       </c>
       <c r="P72">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="73" spans="1:16">
+        <v>1</v>
+      </c>
+      <c r="Q72">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17">
       <c r="A73">
         <v>72</v>
       </c>
@@ -4033,46 +4252,49 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>0</v>
+        <v>20.65087216216216</v>
       </c>
       <c r="E73">
         <v>0</v>
       </c>
       <c r="F73">
-        <v>6.762383333333334</v>
+        <v>15.53102677999999</v>
       </c>
       <c r="G73">
-        <v>0</v>
+        <v>3.778331917499999</v>
       </c>
       <c r="H73">
-        <v>0.64428</v>
+        <v>0.678795</v>
       </c>
       <c r="I73">
-        <v>0</v>
+        <v>20.15087216216216</v>
       </c>
       <c r="J73">
-        <v>0</v>
+        <v>234.671309704783</v>
       </c>
       <c r="K73">
         <v>0</v>
       </c>
       <c r="L73">
-        <v>0.7669999999999999</v>
+        <v>15.11332767</v>
       </c>
       <c r="M73">
-        <v>0</v>
+        <v>0.767</v>
       </c>
       <c r="N73">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O73">
         <v>-0</v>
       </c>
       <c r="P73">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="74" spans="1:16">
+        <v>1</v>
+      </c>
+      <c r="Q73">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17">
       <c r="A74">
         <v>73</v>
       </c>
@@ -4083,46 +4305,49 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>0</v>
+        <v>20.65087216216216</v>
       </c>
       <c r="E74">
         <v>0</v>
       </c>
       <c r="F74">
-        <v>6.118103333333334</v>
+        <v>18.63056369749999</v>
       </c>
       <c r="G74">
-        <v>0</v>
+        <v>3.778331917499999</v>
       </c>
       <c r="H74">
-        <v>0.63336</v>
+        <v>0.6672900000000002</v>
       </c>
       <c r="I74">
-        <v>0</v>
+        <v>20.15087216216216</v>
       </c>
       <c r="J74">
-        <v>0</v>
+        <v>234.671309704783</v>
       </c>
       <c r="K74">
         <v>0</v>
       </c>
       <c r="L74">
-        <v>0.754</v>
+        <v>15.11332767</v>
       </c>
       <c r="M74">
-        <v>0</v>
+        <v>0.7540000000000002</v>
       </c>
       <c r="N74">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O74">
         <v>-0</v>
       </c>
       <c r="P74">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="75" spans="1:16">
+        <v>1</v>
+      </c>
+      <c r="Q74">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17">
       <c r="A75">
         <v>74</v>
       </c>
@@ -4133,46 +4358,49 @@
         <v>0</v>
       </c>
       <c r="D75">
-        <v>34.8</v>
+        <v>20.65087216216216</v>
       </c>
       <c r="E75">
         <v>0</v>
       </c>
       <c r="F75">
-        <v>5.484743333333334</v>
+        <v>21.74160561499999</v>
       </c>
       <c r="G75">
-        <v>6.526800000000001</v>
+        <v>3.778331917499999</v>
       </c>
       <c r="H75">
-        <v>0.62244</v>
+        <v>0.655785</v>
       </c>
       <c r="I75">
-        <v>34.3</v>
+        <v>20.15087216216216</v>
       </c>
       <c r="J75">
-        <v>0</v>
+        <v>234.671309704783</v>
       </c>
       <c r="K75">
-        <v>26.1072</v>
+        <v>0</v>
       </c>
       <c r="L75">
+        <v>15.11332767</v>
+      </c>
+      <c r="M75">
         <v>0.741</v>
       </c>
-      <c r="M75">
-        <v>0</v>
-      </c>
       <c r="N75">
+        <v>0</v>
+      </c>
+      <c r="O75">
+        <v>-0</v>
+      </c>
+      <c r="P75">
         <v>1</v>
       </c>
-      <c r="O75">
-        <v>1</v>
-      </c>
-      <c r="P75">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="76" spans="1:16">
+      <c r="Q75">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17">
       <c r="A76">
         <v>75</v>
       </c>
@@ -4183,46 +4411,49 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>0</v>
+        <v>20.65087216216216</v>
       </c>
       <c r="E76">
         <v>0</v>
       </c>
       <c r="F76">
-        <v>11.38910333333333</v>
+        <v>24.86415253249999</v>
       </c>
       <c r="G76">
-        <v>0</v>
+        <v>3.778331917499999</v>
       </c>
       <c r="H76">
-        <v>0.61152</v>
+        <v>0.64428</v>
       </c>
       <c r="I76">
-        <v>0</v>
+        <v>20.15087216216216</v>
       </c>
       <c r="J76">
-        <v>0</v>
+        <v>234.671309704783</v>
       </c>
       <c r="K76">
         <v>0</v>
       </c>
       <c r="L76">
+        <v>15.11332767</v>
+      </c>
+      <c r="M76">
         <v>0.728</v>
       </c>
-      <c r="M76">
-        <v>0</v>
-      </c>
       <c r="N76">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O76">
         <v>-0</v>
       </c>
       <c r="P76">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="77" spans="1:16">
+        <v>1</v>
+      </c>
+      <c r="Q76">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17">
       <c r="A77">
         <v>76</v>
       </c>
@@ -4233,46 +4464,49 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>0</v>
+        <v>20.65087216216216</v>
       </c>
       <c r="E77">
         <v>0</v>
       </c>
       <c r="F77">
-        <v>10.77758333333333</v>
+        <v>27.99820444999999</v>
       </c>
       <c r="G77">
-        <v>0</v>
+        <v>3.778331917499999</v>
       </c>
       <c r="H77">
-        <v>0.6006000000000001</v>
+        <v>0.6327750000000002</v>
       </c>
       <c r="I77">
-        <v>0</v>
+        <v>20.15087216216216</v>
       </c>
       <c r="J77">
-        <v>0</v>
+        <v>234.671309704783</v>
       </c>
       <c r="K77">
         <v>0</v>
       </c>
       <c r="L77">
+        <v>15.11332767</v>
+      </c>
+      <c r="M77">
         <v>0.7150000000000002</v>
       </c>
-      <c r="M77">
-        <v>0</v>
-      </c>
       <c r="N77">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O77">
         <v>-0</v>
       </c>
       <c r="P77">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="78" spans="1:16">
+        <v>1</v>
+      </c>
+      <c r="Q77">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17">
       <c r="A78">
         <v>77</v>
       </c>
@@ -4283,46 +4517,49 @@
         <v>0</v>
       </c>
       <c r="D78">
-        <v>0</v>
+        <v>20.65087216216216</v>
       </c>
       <c r="E78">
         <v>0</v>
       </c>
       <c r="F78">
-        <v>10.17698333333333</v>
+        <v>31.14376136749999</v>
       </c>
       <c r="G78">
-        <v>0</v>
+        <v>3.778331917499999</v>
       </c>
       <c r="H78">
-        <v>0.58968</v>
+        <v>0.62127</v>
       </c>
       <c r="I78">
-        <v>0</v>
+        <v>20.15087216216216</v>
       </c>
       <c r="J78">
-        <v>0</v>
+        <v>234.671309704783</v>
       </c>
       <c r="K78">
         <v>0</v>
       </c>
       <c r="L78">
+        <v>15.11332767</v>
+      </c>
+      <c r="M78">
         <v>0.702</v>
       </c>
-      <c r="M78">
-        <v>0</v>
-      </c>
       <c r="N78">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O78">
         <v>-0</v>
       </c>
       <c r="P78">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="79" spans="1:16">
+        <v>1</v>
+      </c>
+      <c r="Q78">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17">
       <c r="A79">
         <v>78</v>
       </c>
@@ -4333,46 +4570,49 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>0</v>
+        <v>20.65087216216216</v>
       </c>
       <c r="E79">
         <v>0</v>
       </c>
       <c r="F79">
-        <v>9.587303333333335</v>
+        <v>34.30082328499999</v>
       </c>
       <c r="G79">
-        <v>0</v>
+        <v>3.778331917499999</v>
       </c>
       <c r="H79">
-        <v>0.5787600000000001</v>
+        <v>0.609765</v>
       </c>
       <c r="I79">
-        <v>0</v>
+        <v>20.15087216216216</v>
       </c>
       <c r="J79">
-        <v>0</v>
+        <v>234.671309704783</v>
       </c>
       <c r="K79">
         <v>0</v>
       </c>
       <c r="L79">
+        <v>15.11332767</v>
+      </c>
+      <c r="M79">
         <v>0.6890000000000001</v>
       </c>
-      <c r="M79">
-        <v>0</v>
-      </c>
       <c r="N79">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O79">
         <v>-0</v>
       </c>
       <c r="P79">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="80" spans="1:16">
+        <v>1</v>
+      </c>
+      <c r="Q79">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17">
       <c r="A80">
         <v>79</v>
       </c>
@@ -4383,46 +4623,49 @@
         <v>0</v>
       </c>
       <c r="D80">
-        <v>0</v>
+        <v>20.65087216216216</v>
       </c>
       <c r="E80">
         <v>0</v>
       </c>
       <c r="F80">
-        <v>9.008543333333334</v>
+        <v>37.46939020249999</v>
       </c>
       <c r="G80">
-        <v>0</v>
+        <v>3.778331917499999</v>
       </c>
       <c r="H80">
-        <v>0.5678400000000001</v>
+        <v>0.5982600000000001</v>
       </c>
       <c r="I80">
-        <v>0</v>
+        <v>20.15087216216216</v>
       </c>
       <c r="J80">
-        <v>0</v>
+        <v>234.671309704783</v>
       </c>
       <c r="K80">
         <v>0</v>
       </c>
       <c r="L80">
+        <v>15.11332767</v>
+      </c>
+      <c r="M80">
         <v>0.6760000000000002</v>
       </c>
-      <c r="M80">
-        <v>0</v>
-      </c>
       <c r="N80">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O80">
         <v>-0</v>
       </c>
       <c r="P80">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="81" spans="1:16">
+        <v>1</v>
+      </c>
+      <c r="Q80">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17">
       <c r="A81">
         <v>80</v>
       </c>
@@ -4433,46 +4676,49 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>0</v>
+        <v>20.65087216216216</v>
       </c>
       <c r="E81">
         <v>0</v>
       </c>
       <c r="F81">
-        <v>8.440703333333333</v>
+        <v>40.64946211999999</v>
       </c>
       <c r="G81">
-        <v>0</v>
+        <v>3.778331917499999</v>
       </c>
       <c r="H81">
-        <v>0.55692</v>
+        <v>0.586755</v>
       </c>
       <c r="I81">
-        <v>0</v>
+        <v>20.15087216216216</v>
       </c>
       <c r="J81">
-        <v>0</v>
+        <v>234.671309704783</v>
       </c>
       <c r="K81">
         <v>0</v>
       </c>
       <c r="L81">
-        <v>0.6629999999999999</v>
+        <v>15.11332767</v>
       </c>
       <c r="M81">
-        <v>0</v>
+        <v>0.663</v>
       </c>
       <c r="N81">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O81">
         <v>-0</v>
       </c>
       <c r="P81">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="82" spans="1:16">
+        <v>1</v>
+      </c>
+      <c r="Q81">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17">
       <c r="A82">
         <v>81</v>
       </c>
@@ -4483,46 +4729,49 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>0</v>
+        <v>20.65087216216216</v>
       </c>
       <c r="E82">
         <v>0</v>
       </c>
       <c r="F82">
-        <v>7.883783333333333</v>
+        <v>43.84103903749999</v>
       </c>
       <c r="G82">
-        <v>0</v>
+        <v>3.778331917499999</v>
       </c>
       <c r="H82">
-        <v>0.546</v>
+        <v>0.57525</v>
       </c>
       <c r="I82">
-        <v>0</v>
+        <v>20.15087216216216</v>
       </c>
       <c r="J82">
-        <v>0</v>
+        <v>234.671309704783</v>
       </c>
       <c r="K82">
         <v>0</v>
       </c>
       <c r="L82">
+        <v>15.11332767</v>
+      </c>
+      <c r="M82">
         <v>0.65</v>
       </c>
-      <c r="M82">
-        <v>0</v>
-      </c>
       <c r="N82">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O82">
         <v>-0</v>
       </c>
       <c r="P82">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="83" spans="1:16">
+        <v>1</v>
+      </c>
+      <c r="Q82">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17">
       <c r="A83">
         <v>82</v>
       </c>
@@ -4533,46 +4782,49 @@
         <v>0</v>
       </c>
       <c r="D83">
-        <v>0</v>
+        <v>20.65087216216216</v>
       </c>
       <c r="E83">
         <v>0</v>
       </c>
       <c r="F83">
-        <v>7.337783333333332</v>
+        <v>47.04412095499999</v>
       </c>
       <c r="G83">
-        <v>0</v>
+        <v>3.778331917499999</v>
       </c>
       <c r="H83">
-        <v>0.5623800000000001</v>
+        <v>0.5925075000000001</v>
       </c>
       <c r="I83">
-        <v>0</v>
+        <v>20.15087216216216</v>
       </c>
       <c r="J83">
-        <v>0</v>
+        <v>234.671309704783</v>
       </c>
       <c r="K83">
         <v>0</v>
       </c>
       <c r="L83">
+        <v>15.11332767</v>
+      </c>
+      <c r="M83">
         <v>0.6695000000000001</v>
       </c>
-      <c r="M83">
-        <v>0</v>
-      </c>
       <c r="N83">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O83">
         <v>-0</v>
       </c>
       <c r="P83">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="84" spans="1:16">
+        <v>1</v>
+      </c>
+      <c r="Q83">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17">
       <c r="A84">
         <v>83</v>
       </c>
@@ -4583,46 +4835,49 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>0</v>
+        <v>20.65087216216216</v>
       </c>
       <c r="E84">
         <v>0</v>
       </c>
       <c r="F84">
-        <v>6.775403333333332</v>
+        <v>50.22994537249999</v>
       </c>
       <c r="G84">
-        <v>0</v>
+        <v>3.778331917499999</v>
       </c>
       <c r="H84">
-        <v>0.5787600000000001</v>
+        <v>0.609765</v>
       </c>
       <c r="I84">
-        <v>0</v>
+        <v>20.15087216216216</v>
       </c>
       <c r="J84">
-        <v>0</v>
+        <v>234.671309704783</v>
       </c>
       <c r="K84">
         <v>0</v>
       </c>
       <c r="L84">
+        <v>15.11332767</v>
+      </c>
+      <c r="M84">
         <v>0.6890000000000001</v>
       </c>
-      <c r="M84">
-        <v>0</v>
-      </c>
       <c r="N84">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O84">
         <v>-0</v>
       </c>
       <c r="P84">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="85" spans="1:16">
+        <v>1</v>
+      </c>
+      <c r="Q84">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17">
       <c r="A85">
         <v>84</v>
       </c>
@@ -4633,46 +4888,49 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <v>0</v>
+        <v>11.25353545148633</v>
       </c>
       <c r="E85">
         <v>0</v>
       </c>
       <c r="F85">
-        <v>6.196643333333332</v>
+        <v>53.39851228999999</v>
       </c>
       <c r="G85">
-        <v>0</v>
+        <v>1.973305070000002</v>
       </c>
       <c r="H85">
-        <v>0.5951400000000001</v>
+        <v>0.6270225000000001</v>
       </c>
       <c r="I85">
-        <v>0</v>
+        <v>10.75353545148633</v>
       </c>
       <c r="J85">
-        <v>0</v>
+        <v>151.3694833874782</v>
       </c>
       <c r="K85">
         <v>0</v>
       </c>
       <c r="L85">
+        <v>7.893220280000008</v>
+      </c>
+      <c r="M85">
         <v>0.7085000000000001</v>
       </c>
-      <c r="M85">
-        <v>0</v>
-      </c>
       <c r="N85">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O85">
         <v>-0</v>
       </c>
       <c r="P85">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="86" spans="1:16">
+        <v>1</v>
+      </c>
+      <c r="Q85">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17">
       <c r="A86">
         <v>85</v>
       </c>
@@ -4683,46 +4941,49 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>0</v>
+        <v>11.25353545148633</v>
       </c>
       <c r="E86">
         <v>0</v>
       </c>
       <c r="F86">
-        <v>5.601503333333333</v>
+        <v>54.74479485999999</v>
       </c>
       <c r="G86">
-        <v>0</v>
+        <v>1.973305070000002</v>
       </c>
       <c r="H86">
-        <v>0.61152</v>
+        <v>0.64428</v>
       </c>
       <c r="I86">
-        <v>0</v>
+        <v>10.75353545148633</v>
       </c>
       <c r="J86">
-        <v>0</v>
+        <v>151.3694833874782</v>
       </c>
       <c r="K86">
         <v>0</v>
       </c>
       <c r="L86">
+        <v>7.893220280000008</v>
+      </c>
+      <c r="M86">
         <v>0.728</v>
       </c>
-      <c r="M86">
-        <v>0</v>
-      </c>
       <c r="N86">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O86">
         <v>-0</v>
       </c>
       <c r="P86">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="87" spans="1:16">
+        <v>1</v>
+      </c>
+      <c r="Q86">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17">
       <c r="A87">
         <v>86</v>
       </c>
@@ -4733,46 +4994,49 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>0</v>
+        <v>11.25353545148633</v>
       </c>
       <c r="E87">
         <v>0</v>
       </c>
       <c r="F87">
-        <v>4.989983333333333</v>
+        <v>56.07381993</v>
       </c>
       <c r="G87">
-        <v>0</v>
+        <v>1.973305070000002</v>
       </c>
       <c r="H87">
-        <v>0.6279</v>
+        <v>0.6615374999999999</v>
       </c>
       <c r="I87">
-        <v>0</v>
+        <v>10.75353545148633</v>
       </c>
       <c r="J87">
-        <v>0</v>
+        <v>151.3694833874782</v>
       </c>
       <c r="K87">
         <v>0</v>
       </c>
       <c r="L87">
-        <v>0.7475000000000001</v>
+        <v>7.893220280000008</v>
       </c>
       <c r="M87">
-        <v>0</v>
+        <v>0.7474999999999999</v>
       </c>
       <c r="N87">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O87">
         <v>-0</v>
       </c>
       <c r="P87">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="88" spans="1:16">
+        <v>1</v>
+      </c>
+      <c r="Q87">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17">
       <c r="A88">
         <v>87</v>
       </c>
@@ -4789,13 +5053,13 @@
         <v>0</v>
       </c>
       <c r="F88">
-        <v>4.362083333333333</v>
+        <v>57.3855875</v>
       </c>
       <c r="G88">
         <v>0</v>
       </c>
       <c r="H88">
-        <v>0.64428</v>
+        <v>0.678795</v>
       </c>
       <c r="I88">
         <v>0</v>
@@ -4807,22 +5071,25 @@
         <v>0</v>
       </c>
       <c r="L88">
-        <v>0.7669999999999999</v>
+        <v>0</v>
       </c>
       <c r="M88">
-        <v>0</v>
+        <v>0.767</v>
       </c>
       <c r="N88">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O88">
         <v>-0</v>
       </c>
       <c r="P88">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="89" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q88">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17">
       <c r="A89">
         <v>88</v>
       </c>
@@ -4839,13 +5106,13 @@
         <v>0</v>
       </c>
       <c r="F89">
-        <v>3.717803333333333</v>
+        <v>56.7067925</v>
       </c>
       <c r="G89">
         <v>0</v>
       </c>
       <c r="H89">
-        <v>0.6606599999999999</v>
+        <v>0.6960525</v>
       </c>
       <c r="I89">
         <v>0</v>
@@ -4857,22 +5124,25 @@
         <v>0</v>
       </c>
       <c r="L89">
-        <v>0.7864999999999999</v>
+        <v>0</v>
       </c>
       <c r="M89">
-        <v>0</v>
+        <v>0.7865</v>
       </c>
       <c r="N89">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O89">
         <v>-0</v>
       </c>
       <c r="P89">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="90" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q89">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17">
       <c r="A90">
         <v>89</v>
       </c>
@@ -4889,13 +5159,13 @@
         <v>0</v>
       </c>
       <c r="F90">
-        <v>3.057143333333333</v>
+        <v>56.01074</v>
       </c>
       <c r="G90">
         <v>0</v>
       </c>
       <c r="H90">
-        <v>0.67704</v>
+        <v>0.71331</v>
       </c>
       <c r="I90">
         <v>0</v>
@@ -4907,22 +5177,25 @@
         <v>0</v>
       </c>
       <c r="L90">
-        <v>0.8059999999999999</v>
+        <v>0</v>
       </c>
       <c r="M90">
-        <v>0</v>
+        <v>0.806</v>
       </c>
       <c r="N90">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O90">
         <v>-0</v>
       </c>
       <c r="P90">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="91" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q90">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17">
       <c r="A91">
         <v>90</v>
       </c>
@@ -4939,13 +5212,13 @@
         <v>0</v>
       </c>
       <c r="F91">
-        <v>2.380103333333333</v>
+        <v>55.29743</v>
       </c>
       <c r="G91">
         <v>0</v>
       </c>
       <c r="H91">
-        <v>0.6934199999999999</v>
+        <v>0.7305674999999999</v>
       </c>
       <c r="I91">
         <v>0</v>
@@ -4957,22 +5230,25 @@
         <v>0</v>
       </c>
       <c r="L91">
+        <v>0</v>
+      </c>
+      <c r="M91">
         <v>0.8254999999999999</v>
       </c>
-      <c r="M91">
-        <v>0</v>
-      </c>
       <c r="N91">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O91">
         <v>-0</v>
       </c>
       <c r="P91">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="92" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q91">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17">
       <c r="A92">
         <v>91</v>
       </c>
@@ -4983,46 +5259,49 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>34.8</v>
+        <v>0</v>
       </c>
       <c r="E92">
         <v>0</v>
       </c>
       <c r="F92">
-        <v>1.686683333333333</v>
+        <v>54.5668625</v>
       </c>
       <c r="G92">
-        <v>6.526800000000001</v>
+        <v>0</v>
       </c>
       <c r="H92">
-        <v>0.7098</v>
+        <v>0.747825</v>
       </c>
       <c r="I92">
-        <v>34.3</v>
+        <v>0</v>
       </c>
       <c r="J92">
         <v>0</v>
       </c>
       <c r="K92">
-        <v>26.1072</v>
+        <v>0</v>
       </c>
       <c r="L92">
+        <v>0</v>
+      </c>
+      <c r="M92">
         <v>0.845</v>
       </c>
-      <c r="M92">
-        <v>0</v>
-      </c>
       <c r="N92">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O92">
-        <v>1</v>
+        <v>-0</v>
       </c>
       <c r="P92">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="93" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q92">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17">
       <c r="A93">
         <v>92</v>
       </c>
@@ -5033,46 +5312,49 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <v>51.6</v>
+        <v>0</v>
       </c>
       <c r="E93">
         <v>0</v>
       </c>
       <c r="F93">
-        <v>7.503683333333333</v>
+        <v>53.81903749999999</v>
       </c>
       <c r="G93">
-        <v>9.7902</v>
+        <v>0</v>
       </c>
       <c r="H93">
-        <v>0.72618</v>
+        <v>0.7650825</v>
       </c>
       <c r="I93">
-        <v>51.1</v>
+        <v>0</v>
       </c>
       <c r="J93">
         <v>0</v>
       </c>
       <c r="K93">
-        <v>39.1608</v>
+        <v>0</v>
       </c>
       <c r="L93">
+        <v>0</v>
+      </c>
+      <c r="M93">
         <v>0.8645</v>
       </c>
-      <c r="M93">
-        <v>0</v>
-      </c>
       <c r="N93">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O93">
-        <v>1</v>
+        <v>-0</v>
       </c>
       <c r="P93">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="94" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q93">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17">
       <c r="A94">
         <v>93</v>
       </c>
@@ -5083,46 +5365,49 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>36.9851565851566</v>
+        <v>0</v>
       </c>
       <c r="E94">
         <v>0</v>
       </c>
       <c r="F94">
-        <v>16.56770333333333</v>
+        <v>53.05395499999999</v>
       </c>
       <c r="G94">
-        <v>6.951266666666669</v>
+        <v>0</v>
       </c>
       <c r="H94">
-        <v>0.7425600000000002</v>
+        <v>0.78234</v>
       </c>
       <c r="I94">
-        <v>36.4851565851566</v>
+        <v>0</v>
       </c>
       <c r="J94">
         <v>0</v>
       </c>
       <c r="K94">
-        <v>27.80506666666668</v>
+        <v>0</v>
       </c>
       <c r="L94">
-        <v>0.8840000000000002</v>
+        <v>0</v>
       </c>
       <c r="M94">
-        <v>0</v>
+        <v>0.884</v>
       </c>
       <c r="N94">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O94">
-        <v>1</v>
+        <v>-0</v>
       </c>
       <c r="P94">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="95" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q94">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17">
       <c r="A95">
         <v>94</v>
       </c>
@@ -5133,46 +5418,49 @@
         <v>0</v>
       </c>
       <c r="D95">
-        <v>51.6</v>
+        <v>0</v>
       </c>
       <c r="E95">
         <v>0</v>
       </c>
       <c r="F95">
-        <v>22.77641</v>
+        <v>52.27161499999999</v>
       </c>
       <c r="G95">
-        <v>9.7902</v>
+        <v>0</v>
       </c>
       <c r="H95">
-        <v>0.7589400000000001</v>
+        <v>0.7995975000000001</v>
       </c>
       <c r="I95">
-        <v>51.1</v>
+        <v>0</v>
       </c>
       <c r="J95">
         <v>0</v>
       </c>
       <c r="K95">
-        <v>39.1608</v>
+        <v>0</v>
       </c>
       <c r="L95">
+        <v>0</v>
+      </c>
+      <c r="M95">
         <v>0.9035000000000001</v>
       </c>
-      <c r="M95">
-        <v>0</v>
-      </c>
       <c r="N95">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O95">
-        <v>1</v>
+        <v>-0</v>
       </c>
       <c r="P95">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="96" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q95">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17">
       <c r="A96">
         <v>95</v>
       </c>
@@ -5183,46 +5471,49 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>51.6</v>
+        <v>0</v>
       </c>
       <c r="E96">
         <v>0</v>
       </c>
       <c r="F96">
-        <v>31.80767</v>
+        <v>51.47201749999999</v>
       </c>
       <c r="G96">
-        <v>9.7902</v>
+        <v>0</v>
       </c>
       <c r="H96">
-        <v>0.77532</v>
+        <v>0.816855</v>
       </c>
       <c r="I96">
-        <v>51.1</v>
+        <v>0</v>
       </c>
       <c r="J96">
         <v>0</v>
       </c>
       <c r="K96">
-        <v>39.1608</v>
+        <v>0</v>
       </c>
       <c r="L96">
+        <v>0</v>
+      </c>
+      <c r="M96">
         <v>0.923</v>
       </c>
-      <c r="M96">
-        <v>0</v>
-      </c>
       <c r="N96">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O96">
-        <v>1</v>
+        <v>-0</v>
       </c>
       <c r="P96">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="97" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q96">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17">
       <c r="A97">
         <v>96</v>
       </c>
@@ -5233,46 +5524,49 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>51.6</v>
+        <v>0</v>
       </c>
       <c r="E97">
         <v>0</v>
       </c>
       <c r="F97">
-        <v>40.82255</v>
+        <v>50.6551625</v>
       </c>
       <c r="G97">
-        <v>9.7902</v>
+        <v>0</v>
       </c>
       <c r="H97">
-        <v>0.7917000000000001</v>
+        <v>0.8341124999999997</v>
       </c>
       <c r="I97">
-        <v>51.1</v>
+        <v>0</v>
       </c>
       <c r="J97">
         <v>0</v>
       </c>
       <c r="K97">
-        <v>39.1608</v>
+        <v>0</v>
       </c>
       <c r="L97">
-        <v>0.9425000000000001</v>
+        <v>0</v>
       </c>
       <c r="M97">
-        <v>0</v>
+        <v>0.9424999999999997</v>
       </c>
       <c r="N97">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O97">
-        <v>1</v>
+        <v>-0</v>
       </c>
       <c r="P97">
-        <v>12.23246965658516</v>
-      </c>
-    </row>
-    <row r="98" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q97">
+        <v>13.3041747224006</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17">
       <c r="A98">
         <v>97</v>
       </c>
@@ -5295,7 +5589,7 @@
         <v>0</v>
       </c>
       <c r="H98">
-        <v>0.7917000000000001</v>
+        <v>0.8341125000000001</v>
       </c>
       <c r="I98">
         <v>0</v>
@@ -5307,19 +5601,22 @@
         <v>0</v>
       </c>
       <c r="L98">
-        <v>0.9425000000000001</v>
+        <v>0</v>
       </c>
       <c r="M98">
-        <v>0</v>
+        <v>0.9425000000000002</v>
       </c>
       <c r="N98">
         <v>0</v>
       </c>
       <c r="O98">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P98">
-        <v>12.23246965658516</v>
+        <v>-0</v>
+      </c>
+      <c r="Q98">
+        <v>13.3041747224006</v>
       </c>
     </row>
   </sheetData>
